--- a/docs/backlogs/backlogs.xlsx
+++ b/docs/backlogs/backlogs.xlsx
@@ -1239,6 +1239,11 @@
   <sheetPr/>
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="6" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="32.4444444444444" customWidth="1"/>
+    <col min="2" max="2" width="33.3333333333333" customWidth="1"/>
+    <col min="3" max="3" width="9" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" ht="15.15" spans="1:5">
       <c r="A1" t="s">
@@ -1257,7 +1262,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="58.35" spans="1:5">
+    <row r="2" ht="15.15" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -1268,7 +1273,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" ht="58.35" spans="1:5">
+    <row r="3" ht="15.15" spans="1:5">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -1279,7 +1284,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" ht="58.35" spans="1:5">
+    <row r="4" ht="15.15" spans="1:5">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -1290,7 +1295,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" ht="58.35" spans="1:5">
+    <row r="5" ht="15.15" spans="1:5">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
@@ -1301,7 +1306,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" ht="43.95" spans="1:5">
+    <row r="6" ht="15.15" spans="1:5">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
@@ -1312,7 +1317,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" ht="58.35" spans="1:5">
+    <row r="7" ht="15.15" spans="1:5">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
